--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260717.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>96,566,000</t>
+          <t>2,807,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,807,000</t>
+          <t>96,566,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>20,642,000</t>
+          <t>1,705,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,705,000</t>
+          <t>20,642,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,564,000</t>
+          <t>7,850,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,850,000</t>
+          <t>5,564,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
